--- a/filer/13863385_mascot.xlsx
+++ b/filer/13863385_mascot.xlsx
@@ -7243,7 +7243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7391,67 +7391,30 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:ReductionOfLeaseCommitments</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:ReductionOfLeaseCommitments</t>
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>14340</v>
+        <v>9967</v>
       </c>
       <c r="E5" s="35" t="n">
-        <v>67180</v>
+        <v>10447</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>38067</v>
+        <v>12001</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>1316</v>
+        <v>67881</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>30684</v>
+        <v>11914</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReductionOfLeaseCommitments</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReductionOfLeaseCommitments</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>9967</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>10447</v>
-      </c>
-      <c r="F6" s="38" t="n">
-        <v>12001</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>67881</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>11914</v>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/13863385_mascot.xlsx
+++ b/filer/13863385_mascot.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/13863385_mascot.xlsx
+++ b/filer/13863385_mascot.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_13863385" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_13863385" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_13863385" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_13863385" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4530,6 +4531,148 @@
       </c>
       <c r="F93" s="13">
         <f>IFERROR($F$30/($F$55+$F$62)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_13863385'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_13863385'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_13863385'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_13863385'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_13863385'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_13863385'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_13863385'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_13863385'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_13863385'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_13863385'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_13863385'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_13863385'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_13863385'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_13863385'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_13863385'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_13863385'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_13863385'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_13863385'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_13863385'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_13863385'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B100">
+        <f>IF(ABS(('pengestrom_raw_13863385'!$B$2+'pengestrom_raw_13863385'!$B$3+'pengestrom_raw_13863385'!$B$4)-'pengestrom_raw_13863385'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13863385'!$B$2+'pengestrom_raw_13863385'!$B$3+'pengestrom_raw_13863385'!$B$4)-'pengestrom_raw_13863385'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>IF(ABS(('pengestrom_raw_13863385'!$C$2+'pengestrom_raw_13863385'!$C$3+'pengestrom_raw_13863385'!$C$4)-'pengestrom_raw_13863385'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13863385'!$C$2+'pengestrom_raw_13863385'!$C$3+'pengestrom_raw_13863385'!$C$4)-'pengestrom_raw_13863385'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>IF(ABS(('pengestrom_raw_13863385'!$D$2+'pengestrom_raw_13863385'!$D$3+'pengestrom_raw_13863385'!$D$4)-'pengestrom_raw_13863385'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13863385'!$D$2+'pengestrom_raw_13863385'!$D$3+'pengestrom_raw_13863385'!$D$4)-'pengestrom_raw_13863385'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>IF(ABS(('pengestrom_raw_13863385'!$E$2+'pengestrom_raw_13863385'!$E$3+'pengestrom_raw_13863385'!$E$4)-'pengestrom_raw_13863385'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13863385'!$E$2+'pengestrom_raw_13863385'!$E$3+'pengestrom_raw_13863385'!$E$4)-'pengestrom_raw_13863385'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>IF(ABS(('pengestrom_raw_13863385'!$F$2+'pengestrom_raw_13863385'!$F$3+'pengestrom_raw_13863385'!$F$4)-'pengestrom_raw_13863385'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13863385'!$F$2+'pengestrom_raw_13863385'!$F$3+'pengestrom_raw_13863385'!$F$4)-'pengestrom_raw_13863385'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4578,354 +4721,354 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1334761</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1656038</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1811275</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1982574</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>2112986</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>681660</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>792537</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>756306</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>799884</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>851623</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>653101</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>863501</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>1054969</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>1182690</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>1261363</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>270702</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>309571</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>421647</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>510656</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>488883</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>126979</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>140368</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>121356</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>123428</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>188951</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>777</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>820</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>255420</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>413562</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>511966</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>548606</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>583529</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>456</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>229</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>20002</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>9435</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>9682</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>4837</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>7883</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>7616</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>7531</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>21034</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>251039</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>405908</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>524352</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>550510</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>572177</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>51995</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>80410</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>103625</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>106428</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>109682</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>199044</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>325498</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>420727</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>444082</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>462495</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>2933</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>3815</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>4248</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>3637</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>3849</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>-114006</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>-95125</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>-147862</v>
       </c>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4972,1064 +5115,1064 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>84116</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>104003</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>124476</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>144871</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>120581</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>99382</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>103633</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>93284</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>79679</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>278955</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>67997</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>65111</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>71403</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>85546</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>89525</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>1232</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>747</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>366</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3091</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>3158</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>73900</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>39819</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>81771</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>151593</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>46322</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>326627</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>313313</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>371300</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>464780</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>538541</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>79653</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>87745</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>90772</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>128870</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>155468</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>90183</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>89768</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>103484</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>138821</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>168244</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>416810</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>403081</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>474784</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>603601</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>706785</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>258282</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>398324</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>267259</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>249715</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>285876</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>63147</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>80576</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>66228</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>71113</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>69648</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>334080</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>576162</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>679602</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>709866</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>772353</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>655509</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>1055062</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1013089</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>1030694</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>1127877</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>223517</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>274480</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>287201</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>326753</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>343944</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>121</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>112</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>3467</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>5164</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>32735</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>820</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1191</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>10074</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>5660</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>27698</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>33833</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>26567</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>29570</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>30422</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>3952</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>287902</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>309254</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>315071</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>369864</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>385190</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n">
         <v>254</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>231</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>209</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>139</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>32406</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>14334</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>94133</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>205366</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <v>255427</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>975817</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>1378650</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>1422293</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>1605924</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>1768494</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>1392627</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>1781731</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>1897077</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>2209525</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>2475279</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>-32538</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>-99718</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>-137785</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>-139101</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>-169785</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>1047004</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>1272502</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>1543229</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>1837311</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>2149806</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>1089966</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>1273284</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>1555944</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>1848710</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>2130521</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>14675</v>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>14683</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>26888</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>31541</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <v>47688</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>25300</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>24805</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>36576</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>40803</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>56534</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>42435</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>33740</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>67811</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>18583</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>8787</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>42435</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>33740</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>67811</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>18583</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>8787</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>9830</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>10680</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>10109</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>9791</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>11266</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n">
         <v>163605</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>85027</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>95186</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>45602</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>91137</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>57104</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>803</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>19812</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>2065</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>4157</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>672</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>140069</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>160619</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>178167</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>196344</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>210395</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>234926</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>449902</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>236746</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>301429</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="17" t="n">
         <v>279437</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>277361</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>483642</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>304557</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>320012</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="F54" s="17" t="n">
         <v>288224</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>1392627</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>1781731</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>1897077</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>2209525</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="17" t="n">
         <v>2475279</v>
       </c>
     </row>
@@ -6039,6 +6182,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>121247</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-9735</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>464735</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>496432</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>390700</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-120189</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-89097</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-154830</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-185653</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-182318</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-56751</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>80760</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-230106</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-199546</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-158321</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7237,7 +7502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
